--- a/artfynd/A 2256-2024 artfynd.xlsx
+++ b/artfynd/A 2256-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2256-2024 artfynd.xlsx
+++ b/artfynd/A 2256-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>66481789</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455354.6894991441</v>
+        <v>455355</v>
       </c>
       <c r="R2" t="n">
-        <v>7074070.370032913</v>
+        <v>7074070</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2009-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,16 +780,11 @@
         <v>89603711</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455437.1384233451</v>
+        <v>455437</v>
       </c>
       <c r="R3" t="n">
-        <v>7073890.131773623</v>
+        <v>7073890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89603739</v>
+        <v>89603717</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455436.0966062522</v>
+        <v>455436</v>
       </c>
       <c r="R4" t="n">
-        <v>7073879.092522057</v>
+        <v>7073879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,21 +946,11 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1004,6 +959,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Rönn</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1024,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89603717</v>
+        <v>89603739</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +995,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455436.0966062522</v>
+        <v>455436</v>
       </c>
       <c r="R5" t="n">
-        <v>7073879.092522057</v>
+        <v>7073879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,21 +1052,11 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1120,11 +1065,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 2256-2024 artfynd.xlsx
+++ b/artfynd/A 2256-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66481789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603717</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,8 +1102,19 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603739</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>